--- a/Employee_Reports_wi48/Mohomed Minnas Mohomed Ramees Q0582.xlsx
+++ b/Employee_Reports_wi48/Mohomed Minnas Mohomed Ramees Q0582.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1128,9 +1128,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -1142,11 +1154,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1191,11 +1203,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1228,11 +1240,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
